--- a/xls/square_high_un_16_tri3_13.xlsx
+++ b/xls/square_high_un_16_tri3_13.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>238</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>340</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>174</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>906</v>
+      </c>
+      <c r="I11">
+        <v>-1.0623468455970224</v>
+      </c>
+      <c r="J11">
+        <v>-1.5668673644922588</v>
+      </c>
+      <c r="K11">
+        <v>-0.6138777922078189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>238</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
+        <v>340</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>209</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12">
+        <v>1104</v>
+      </c>
+      <c r="I12">
+        <v>-1.6135780211943171</v>
+      </c>
+      <c r="J12">
+        <v>-1.9386439905443726</v>
+      </c>
+      <c r="K12">
+        <v>-0.9162929988029891</v>
+      </c>
+    </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>11</v>
